--- a/real_estate_forms/010_real_estate_covid_19_compliance_questionnaire--real_estate_forms.xlsx
+++ b/real_estate_forms/010_real_estate_covid_19_compliance_questionnaire--real_estate_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Property Access Time</t>
+          <t>Property Access Time In Hours</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Property Access Frequency</t>
+          <t>Property Access Frequency In Days</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Visitor Pledge</t>
+          <t>Visitor Pledge Frequency</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Property Access Time</t>
+          <t>Property Access Time In Seconds</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Visitor Pledge</t>
+          <t>Visitor Pledge Frequency In Days</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>property_access_time_in_seconds</t>
+          <t>property_access_time_in_seconds_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Property Access Time</t>
+          <t>Property Access Time In Seconds 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'no_covid-19_symptoms'}</t>
+          <t>no_covid-19_symptoms</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'No COVID-19 symptoms'}</t>
+          <t>No COVID-19 symptoms</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'have_covid-19'}</t>
+          <t>have_covid-19</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Have COVID-19'}</t>
+          <t>Have COVID-19</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'have_had_covid-19_recently'}</t>
+          <t>have_had_covid-19_recently</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Have had COVID-19 recently'}</t>
+          <t>Have had COVID-19 recently</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Unsure'}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Not Sure'}</t>
+          <t>Not Sure</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'partially_vaccinated'}</t>
+          <t>partially_vaccinated</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Partially Vaccinated'}</t>
+          <t>Partially Vaccinated</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'fully_vaccinated'}</t>
+          <t>fully_vaccinated</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Fully Vaccinated'}</t>
+          <t>Fully Vaccinated</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'no_test_done'}</t>
+          <t>no_test_done</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'No Test Done'}</t>
+          <t>No Test Done</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'negative'}</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Negative'}</t>
+          <t>Negative</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'positive'}</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Positive'}</t>
+          <t>Positive</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'i_will_follow_the_instructions_of_the_property_manager'}</t>
+          <t>i_will_follow_the_instructions_of_the_property_manager</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'I will follow the instructions of the property manager'}</t>
+          <t>I will follow the instructions of the property manager</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'i_will_take_necessary_precautions_to_prevent_the_spread_of_covid-19'}</t>
+          <t>i_will_take_necessary_precautions_to_prevent_the_spread_of_covid-19</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'I will take necessary precautions to prevent the spread of COVID-19'}</t>
+          <t>I will take necessary precautions to prevent the spread of COVID-19</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Not Sure'}</t>
+          <t>Not Sure</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'less_than_once_a_week'}</t>
+          <t>less_than_once_a_week</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Less than once a week'}</t>
+          <t>Less than once a week</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'1-2_times_a_week'}</t>
+          <t>1-2_times_a_week</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': '1-2 times a week'}</t>
+          <t>1-2 times a week</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'3-4_times_a_week'}</t>
+          <t>3-4_times_a_week</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': '3-4 times a week'}</t>
+          <t>3-4 times a week</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'5-6_times_a_week'}</t>
+          <t>5-6_times_a_week</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': '5-6 times a week'}</t>
+          <t>5-6 times a week</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'every_day'}</t>
+          <t>every_day</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Every day'}</t>
+          <t>Every day</t>
         </is>
       </c>
     </row>
